--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-03T13:50:07+00:00</t>
+    <t>2024-07-03T13:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-03T13:52:48+00:00</t>
+    <t>2024-07-03T13:54:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-03T13:54:46+00:00</t>
+    <t>2024-07-04T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-04T13:52:01+00:00</t>
+    <t>2024-07-09T12:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T12:16:32+00:00</t>
+    <t>2024-07-09T12:36:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T12:36:00+00:00</t>
+    <t>2024-07-12T14:55:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T14:55:46+00:00</t>
+    <t>2024-07-17T06:26:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T06:26:56+00:00</t>
+    <t>2024-07-17T06:40:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T06:40:14+00:00</t>
+    <t>2024-07-17T06:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T06:51:58+00:00</t>
+    <t>2024-07-17T17:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T17:08:26+00:00</t>
+    <t>2024-07-17T17:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T17:33:21+00:00</t>
+    <t>2024-07-18T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-18T16:11:48+00:00</t>
+    <t>2024-07-19T13:28:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-19T13:28:45+00:00</t>
+    <t>2024-07-19T14:51:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T08:03:17+00:00</t>
+    <t>2025-12-11T11:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-11T11:06:01+00:00</t>
+    <t>2026-05-06T06:43:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
+++ b/main/ig/ValueSet-sas-sos-valueset-participant-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T06:43:41+00:00</t>
+    <t>2026-05-07T11:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
